--- a/data/trans_orig/IP07C08-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C08-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haberse ayudado entre los amigos en 2007 (tasa de respuesta: 89,69%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2007 (tasa de respuesta: 89,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>10125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>19707</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>15923</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>19280</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32592</t>
+          <t>31895</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>42,5%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13739</t>
+          <t>13729</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23941</t>
+          <t>23732</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16029</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24887</t>
+          <t>25519</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31898</t>
+          <t>32508</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46263</t>
+          <t>46340</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,75%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>702</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15199</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>8564</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>17060</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15031</t>
+          <t>14819</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17866</t>
+          <t>17920</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29593</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13683</t>
+          <t>14133</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19263</t>
+          <t>19695</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18734</t>
+          <t>19121</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30332</t>
+          <t>30743</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>56,23%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>681</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13282</t>
+          <t>13430</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14769</t>
+          <t>14613</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26220</t>
+          <t>25920</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22067</t>
+          <t>21881</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35653</t>
+          <t>36601</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>46,1%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12046</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21097</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19437</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30435</t>
+          <t>30579</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34632</t>
+          <t>34382</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48989</t>
+          <t>49178</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,94%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>461</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11282</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27620</t>
+          <t>27997</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42475</t>
+          <t>42506</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29305</t>
+          <t>28963</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44029</t>
+          <t>43027</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60713</t>
+          <t>61010</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81658</t>
+          <t>81472</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,66%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30285</t>
+          <t>31279</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45412</t>
+          <t>45678</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27803</t>
+          <t>28548</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42399</t>
+          <t>42483</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63909</t>
+          <t>64000</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>85424</t>
+          <t>84929</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,73%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16614</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14962</t>
+          <t>15148</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14546</t>
+          <t>14648</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27586</t>
+          <t>27429</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>636</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,42 +3172,42 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2636</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>6162</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>3,68%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>2636</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>5975</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14251</t>
+          <t>15021</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25517</t>
+          <t>26116</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>16040</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27388</t>
+          <t>27766</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>33350</t>
+          <t>33702</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>49738</t>
+          <t>49846</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,34%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14258</t>
+          <t>14014</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25317</t>
+          <t>25152</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21910</t>
+          <t>21836</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33836</t>
+          <t>34370</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>38877</t>
+          <t>39729</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>55810</t>
+          <t>55879</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,83%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18992</t>
+          <t>18897</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14383</t>
+          <t>14125</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>27862</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5755</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>14757</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>16888</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>16926</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>29289</t>
+          <t>29302</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>21855</t>
+          <t>21820</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>30889</t>
+          <t>30596</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11813</t>
+          <t>12482</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20665</t>
+          <t>21369</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>36423</t>
+          <t>35803</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>49316</t>
+          <t>49335</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,77%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7436</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>89921</t>
+          <t>89061</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>114502</t>
+          <t>114149</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>97609</t>
+          <t>98183</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>125098</t>
+          <t>124596</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>195243</t>
+          <t>195499</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>230543</t>
+          <t>231009</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>116210</t>
+          <t>116318</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>140833</t>
+          <t>142736</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>127006</t>
+          <t>127583</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>153964</t>
+          <t>154077</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>250545</t>
+          <t>250870</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>288266</t>
+          <t>286576</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,53%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>23511</t>
+          <t>22579</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>39848</t>
+          <t>39646</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>27273</t>
+          <t>27313</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>45752</t>
+          <t>45503</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>55457</t>
+          <t>53310</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>80165</t>
+          <t>79720</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haberse ayudado entre los amigos en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11309</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21837</t>
+          <t>21384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15442</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24616</t>
+          <t>24331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29233</t>
+          <t>28898</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43075</t>
+          <t>43096</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,2%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22553</t>
+          <t>22854</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14491</t>
+          <t>14933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21802</t>
+          <t>22245</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35216</t>
+          <t>35174</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,95%</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5986,42 +5986,42 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>9,69%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4131</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8254</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>12,08%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4131</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1415</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8003</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>12,08%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10722</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23011</t>
+          <t>22513</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10274</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19838</t>
+          <t>19218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26299</t>
+          <t>25701</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39721</t>
+          <t>38880</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16067</t>
+          <t>15840</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>17990</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18744</t>
+          <t>18862</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31803</t>
+          <t>32471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,96%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22421</t>
+          <t>22018</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11509</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20698</t>
+          <t>20812</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26764</t>
+          <t>26801</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40308</t>
+          <t>40486</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,44%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17515</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28059</t>
+          <t>28268</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>13135</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25406</t>
+          <t>24707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39082</t>
+          <t>38761</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,12%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12518</t>
+          <t>12876</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30873</t>
+          <t>31112</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45616</t>
+          <t>46032</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39130</t>
+          <t>39899</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55022</t>
+          <t>55441</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74154</t>
+          <t>74814</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96942</t>
+          <t>96559</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,97%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29834</t>
+          <t>28952</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44360</t>
+          <t>44149</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27765</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43246</t>
+          <t>42640</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>61853</t>
+          <t>61725</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83014</t>
+          <t>82823</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,43%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12558</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>7775</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>18779</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14095</t>
+          <t>14482</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>28014</t>
+          <t>28534</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7588</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>24370</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38706</t>
+          <t>39148</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24327</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>38177</t>
+          <t>37764</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>51897</t>
+          <t>53106</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>72449</t>
+          <t>73498</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>50,33%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27415</t>
+          <t>27719</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>41805</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24500</t>
+          <t>25436</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38638</t>
+          <t>39946</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>56139</t>
+          <t>55684</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>76753</t>
+          <t>76101</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,11%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>9881</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>11253</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17979</t>
+          <t>18269</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -8807,62 +8807,62 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>5128</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>5007</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3149</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>3240</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>722</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>13548</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>10468</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>19133</t>
+          <t>20036</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>18042</t>
+          <t>18295</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,6%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16118</t>
+          <t>15826</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>23179</t>
+          <t>22483</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>23510</t>
+          <t>23390</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>35902</t>
+          <t>36269</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,63%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>583</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8767</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>116799</t>
+          <t>116606</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>145644</t>
+          <t>144894</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>129815</t>
+          <t>130514</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>158169</t>
+          <t>159435</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>254633</t>
+          <t>251797</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>294070</t>
+          <t>293375</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,92%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>120462</t>
+          <t>121678</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>150018</t>
+          <t>150206</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>104651</t>
+          <t>103345</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>131732</t>
+          <t>130601</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>231915</t>
+          <t>234133</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>272493</t>
+          <t>274700</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,81%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>14978</t>
+          <t>15273</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>29141</t>
+          <t>29742</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>28816</t>
+          <t>28737</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>45958</t>
+          <t>46588</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>47858</t>
+          <t>47804</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>71240</t>
+          <t>70567</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>8812</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>13520</t>
+          <t>13993</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>10297</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haberse ayudado entre los amigos en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14230</t>
+          <t>14473</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23407</t>
+          <t>23112</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18521</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28217</t>
+          <t>28203</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35459</t>
+          <t>35414</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49539</t>
+          <t>48982</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>69,93%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8779</t>
+          <t>8743</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17787</t>
+          <t>17608</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14777</t>
+          <t>14467</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16258</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29258</t>
+          <t>29737</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8379</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8754</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>17284</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28937</t>
+          <t>28334</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>22164</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34008</t>
+          <t>33281</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42336</t>
+          <t>42940</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58706</t>
+          <t>59266</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,51%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12373</t>
+          <t>12369</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23241</t>
+          <t>23544</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11674</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22976</t>
+          <t>23282</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27483</t>
+          <t>27664</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43527</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>11671</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>724</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14430</t>
+          <t>14604</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -11887,7 +11887,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8875</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17667</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13485</t>
+          <t>13345</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>23455</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23989</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37891</t>
+          <t>37938</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,24%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15594</t>
+          <t>15469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13476</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23012</t>
+          <t>23518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23357</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36845</t>
+          <t>36304</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>53,82%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2297</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45770</t>
+          <t>45938</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63465</t>
+          <t>63717</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39859</t>
+          <t>40167</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56661</t>
+          <t>56446</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89948</t>
+          <t>90771</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114914</t>
+          <t>115028</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,75%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32718</t>
+          <t>32889</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50074</t>
+          <t>49511</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30601</t>
+          <t>31161</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47514</t>
+          <t>46503</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>68295</t>
+          <t>67710</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>91332</t>
+          <t>91592</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,6%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>9621</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21753</t>
+          <t>21174</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15968</t>
+          <t>15768</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17442</t>
+          <t>16944</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33197</t>
+          <t>32329</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25679</t>
+          <t>26127</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40710</t>
+          <t>40646</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23837</t>
+          <t>23155</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>36831</t>
+          <t>37692</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>53077</t>
+          <t>53911</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>73546</t>
+          <t>73512</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,42%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28233</t>
+          <t>28512</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42589</t>
+          <t>42702</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18724</t>
+          <t>18579</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31793</t>
+          <t>31807</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>50865</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>69918</t>
+          <t>70693</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>17060</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10265</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23259</t>
+          <t>23019</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>696</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>12958</t>
+          <t>12808</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22775</t>
+          <t>22839</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16035</t>
+          <t>16156</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>25883</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>31824</t>
+          <t>32386</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>46307</t>
+          <t>46482</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,92%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15798</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15075</t>
+          <t>15387</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>14588</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27670</t>
+          <t>28287</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12593</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>613</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>145429</t>
+          <t>147311</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>176843</t>
+          <t>176318</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>153422</t>
+          <t>154673</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>183361</t>
+          <t>185249</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>307972</t>
+          <t>307729</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>352650</t>
+          <t>350852</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>113247</t>
+          <t>115258</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>143831</t>
+          <t>144052</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>105198</t>
+          <t>102527</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>134896</t>
+          <t>132434</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>226465</t>
+          <t>227585</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>267940</t>
+          <t>270843</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,2%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>24866</t>
+          <t>25408</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>42516</t>
+          <t>42712</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>25119</t>
+          <t>24406</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>42636</t>
+          <t>43519</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>55745</t>
+          <t>54233</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>79810</t>
+          <t>80741</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>696</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>6384</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>13410</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>16598</t>
+          <t>15925</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>546</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
